--- a/data/excel/camiones_puertos.xlsx
+++ b/data/excel/camiones_puertos.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1024"/>
+  <dimension ref="A1:M1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42373,6 +42373,47 @@
       </c>
       <c r="M1024" t="n">
         <v>313</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1025" t="n">
+        <v>6169</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>128</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>1391</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>1237</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>2310</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>93</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>204</v>
+      </c>
+      <c r="K1025" t="n">
+        <v>2318</v>
+      </c>
+      <c r="L1025" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1025" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -42433,7 +42474,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/logistica/_archivos/000023_Posici%C3%B3n%20de%20Camiones%20y%20Vagones/000020_Entrada%20diaria%20de%20camiones%20y%20vagones%20a%20puertos,%20f%C3%A1bricas%20y%20molinos%20(por%20zona%20portuaria%20y%20por%20producto).php https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_enero_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_febrero_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_marzo_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_abril_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_mayo_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_junio_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_julio_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_agosto_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_septiembre_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_octubre_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_noviembre_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2024/total_mensual_diciembre_2024.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_enero_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_feb_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_mar_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_abr_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_may_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_jun_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_jul_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_ago_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_sep_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_oct_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_nov_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2025/total_mensual_dic_2025.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_ene_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_feb_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_mar_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_abr_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_may_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_jun_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_jul_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_ago_2026.pdf https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_sep_2026.pdf</t>
+          <t>https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/logistica/_archivos/000023_Posici%C3%B3n%20de%20Camiones%20y%20Vagones/000020_Entrada%20diaria%20de%20camiones%20y%20vagones%20a%20puertos,%20f%C3%A1bricas%20y%20molinos%20(por%20zona%20portuaria%20y%20por%20producto).php https://www.magyp.gob.ar/sitio/areas/ss_mercados_agropecuarios/informes/entrada_camiones/2026/total_mensual_sep_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -42445,7 +42486,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T21:01:37Z</t>
+          <t>2026-10-20T18:08:31Z</t>
         </is>
       </c>
     </row>
@@ -42457,7 +42498,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos.xlsx
+++ b/data/excel/camiones_puertos.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1025"/>
+  <dimension ref="A1:M1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42414,6 +42414,47 @@
       </c>
       <c r="M1025" t="n">
         <v>112</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1026" t="n">
+        <v>6545</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>4240</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>176</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>683</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>1446</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>1249</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>2650</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>80</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>186</v>
+      </c>
+      <c r="K1026" t="n">
+        <v>2373</v>
+      </c>
+      <c r="L1026" t="n">
+        <v>7</v>
+      </c>
+      <c r="M1026" t="n">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -42486,7 +42527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T18:08:31Z</t>
+          <t>2026-10-21T18:44:48Z</t>
         </is>
       </c>
     </row>
@@ -42498,7 +42539,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos.xlsx
+++ b/data/excel/camiones_puertos.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1026"/>
+  <dimension ref="A1:M1027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42455,6 +42455,47 @@
       </c>
       <c r="M1026" t="n">
         <v>187</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1027" t="n">
+        <v>6681</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>4764</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>173</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>536</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>1208</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>1177</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>2599</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>80</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>195</v>
+      </c>
+      <c r="K1027" t="n">
+        <v>2596</v>
+      </c>
+      <c r="L1027" t="n">
+        <v>34</v>
+      </c>
+      <c r="M1027" t="n">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -42527,7 +42568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T18:44:48Z</t>
+          <t>2026-10-23T05:23:48Z</t>
         </is>
       </c>
     </row>
@@ -42539,7 +42580,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos.xlsx
+++ b/data/excel/camiones_puertos.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1027"/>
+  <dimension ref="A1:M1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42496,6 +42496,47 @@
       </c>
       <c r="M1027" t="n">
         <v>220</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1028" t="n">
+        <v>6665</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>4744</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>151</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>542</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>1228</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>1153</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>2659</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>79</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>107</v>
+      </c>
+      <c r="K1028" t="n">
+        <v>2618</v>
+      </c>
+      <c r="L1028" t="n">
+        <v>49</v>
+      </c>
+      <c r="M1028" t="n">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -42568,7 +42609,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23T05:23:48Z</t>
+          <t>2026-10-24T05:02:43Z</t>
         </is>
       </c>
     </row>
@@ -42580,7 +42621,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
